--- a/data/attendance/ECOLE_نذير_1_ثانوي.xlsx
+++ b/data/attendance/ECOLE_نذير_1_ثانوي.xlsx
@@ -73,12 +73,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <t>student_id:a0d37926-540f-4a05-bf21-c90dd19cdc5d</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <t>student_id:95f465b6-e052-4fcd-a172-e76925bac6e4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <t>student_id:0c995de5-da83-400b-8300-255869307db6</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <t>student_id:33da90bb-f29f-4790-804c-d5e51cd4ad36</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <t>student_id:2ebf8519-efac-4f29-8c34-3f1c59733309</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <t>student_id:5e929a94-081b-46bc-b566-92aa1e99ae24</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>نذير 1 ثانوي  |  ECOLE  |  1AS  |  بوعبدالله نذير</t>
   </si>
@@ -92,6 +134,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -101,6 +146,9 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -128,6 +176,24 @@
     <t>بن كحمان ملاك</t>
   </si>
   <si>
+    <t>بوريو امير</t>
+  </si>
+  <si>
+    <t>بتشيم ليان</t>
+  </si>
+  <si>
+    <t>بوساليا  رنا</t>
+  </si>
+  <si>
+    <t>بوقرن  صالح</t>
+  </si>
+  <si>
+    <t>بن جلول  سارة</t>
+  </si>
+  <si>
+    <t>مقلاتي العكي محمد قصي</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -155,7 +221,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -645,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -671,7 +740,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -681,10 +750,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -726,46 +798,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -773,7 +845,7 @@
         <v>389</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -817,7 +889,7 @@
         <v>743</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -861,7 +933,7 @@
         <v>746</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -905,7 +977,7 @@
         <v>748</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -949,7 +1021,7 @@
         <v>749</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -993,7 +1065,7 @@
         <v>750</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1037,7 +1109,7 @@
         <v>751</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1081,7 +1153,7 @@
         <v>752</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -1117,6 +1189,270 @@
         <v>0</v>
       </c>
       <c r="N12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>840</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>861</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>862</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>863</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>864</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>930</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1136,7 +1472,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -1144,77 +1480,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
